--- a/tracking_forms/025_pivot_data_collection_form--tracking_forms.xlsx
+++ b/tracking_forms/025_pivot_data_collection_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>row_fields</t>
+          <t>aggregation_method</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Row Fields</t>
+          <t>Aggregation Method</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>column_fields</t>
+          <t>aggregation_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Column Fields</t>
+          <t>Aggregation Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>aggregation_details</t>
+          <t>row_fields</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aggregation Details</t>
+          <t>Row Fields</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>data_sources</t>
+          <t>column_fields</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Column Fields</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>aggregation_method</t>
+          <t>data_storage_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aggregation Method</t>
+          <t>Data Storage Location</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>aggregation_type</t>
+          <t>data_security</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aggregation Type</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>aggregation_type</t>
+          <t>data_collection_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aggregation Type</t>
+          <t>Data Collection Frequency</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>row_fields</t>
+          <t>data_collection_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Row Fields</t>
+          <t>Data Collection Method</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>column_fields</t>
+          <t>data_type</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Column Fields</t>
+          <t>Data Type</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>row_fields_type</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Row Fields Type</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>column_fields_type</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Column Fields Type</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,170 +827,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>row_fields_choices</t>
+          <t>aggregation_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>row_fields_choices</t>
+          <t>aggregation_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>column_fields_choices</t>
+          <t>row_fields_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>column_fields_choices</t>
+          <t>row_fields_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>data_sources_choices</t>
+          <t>data_storage_location_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>data_sources_choices</t>
+          <t>data_storage_location_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>on-premises</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>on-premises</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aggregation_method_choices</t>
+          <t>data_security_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>security_measures</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>security measures</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aggregation_method_choices</t>
+          <t>data_security_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aggregation_type_choices</t>
+          <t>data_collection_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aggregation_type_choices</t>
+          <t>data_collection_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>data_collection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>data_collection_method_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>data_collection_method_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>automatic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>data_type_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>data_type_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>data_type_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>row_fields_type_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>row_fields_type_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>row_fields_type_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>column_fields_type_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>column_fields_type_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>column_fields_type_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
